--- a/data/cci/cci-datatype.xlsx
+++ b/data/cci/cci-datatype.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{01B1F068-9F27-4445-8169-AA66171EBCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5DA4676-A240-4A59-9C05-1AB6C01A6147}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{01B1F068-9F27-4445-8169-AA66171EBCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2CFF413-449E-406A-95F1-F3D933B32572}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{43594B32-44C5-1E42-8A39-9DE60AB9706E}"/>
+    <workbookView xWindow="1455" yWindow="135" windowWidth="28800" windowHeight="15285" xr2:uid="{43594B32-44C5-1E42-8A39-9DE60AB9706E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="310">
   <si>
     <t>URI</t>
   </si>
@@ -941,6 +941,15 @@
   </si>
   <si>
     <t>https://climate.esa.int/projects/precursors-for-aerosols-and-ozone/</t>
+  </si>
+  <si>
+    <t>dtype_nh3</t>
+  </si>
+  <si>
+    <t>ammonia</t>
+  </si>
+  <si>
+    <t>NH3</t>
   </si>
 </sst>
 </file>
@@ -1650,7 +1659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7EC9CB0-CBFC-714F-A334-253ED842CDDE}">
-  <dimension ref="A1:BL91"/>
+  <dimension ref="A1:BL92"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" style="4" customWidth="1"/>
@@ -3283,6 +3292,23 @@
         <v>304</v>
       </c>
       <c r="E91" s="15" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="E92" s="15" t="s">
         <v>306</v>
       </c>
     </row>
@@ -3336,6 +3362,7 @@
     <hyperlink ref="E89" r:id="rId46" xr:uid="{20F6A3C3-0D34-F243-AF3B-2F6D9DB0F4EB}"/>
     <hyperlink ref="E90" r:id="rId47" xr:uid="{8F8793D2-4111-9D4A-8A38-8D2824574D36}"/>
     <hyperlink ref="E91" r:id="rId48" xr:uid="{BE7994B6-39AC-456E-B133-6B1058FF6A77}"/>
+    <hyperlink ref="E92" r:id="rId49" xr:uid="{243CF071-55CA-4C95-9A25-06902A0269E2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="1.143700787401575" bottom="1.143700787401575" header="0.75" footer="0.75"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>

--- a/data/cci/cci-datatype.xlsx
+++ b/data/cci/cci-datatype.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{01B1F068-9F27-4445-8169-AA66171EBCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2CFF413-449E-406A-95F1-F3D933B32572}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{01B1F068-9F27-4445-8169-AA66171EBCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D6034F1-9226-4925-9409-8AC7A38D31A9}"/>
   <bookViews>
-    <workbookView xWindow="1455" yWindow="135" windowWidth="28800" windowHeight="15285" xr2:uid="{43594B32-44C5-1E42-8A39-9DE60AB9706E}"/>
+    <workbookView xWindow="9660" yWindow="4650" windowWidth="28800" windowHeight="15345" xr2:uid="{43594B32-44C5-1E42-8A39-9DE60AB9706E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="316">
   <si>
     <t>URI</t>
   </si>
@@ -950,6 +950,24 @@
   </si>
   <si>
     <t>NH3</t>
+  </si>
+  <si>
+    <t>dtype_no2</t>
+  </si>
+  <si>
+    <t>nitrogen dioxide</t>
+  </si>
+  <si>
+    <t>NO2</t>
+  </si>
+  <si>
+    <t>dtype_hcho</t>
+  </si>
+  <si>
+    <t>formaldehyde</t>
+  </si>
+  <si>
+    <t>HCHO</t>
   </si>
 </sst>
 </file>
@@ -1659,7 +1677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7EC9CB0-CBFC-714F-A334-253ED842CDDE}">
-  <dimension ref="A1:BL92"/>
+  <dimension ref="A1:BL94"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" style="4" customWidth="1"/>
@@ -3309,6 +3327,40 @@
         <v>308</v>
       </c>
       <c r="E92" s="15" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="E93" s="15" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="E94" s="15" t="s">
         <v>306</v>
       </c>
     </row>
@@ -3363,6 +3415,7 @@
     <hyperlink ref="E90" r:id="rId47" xr:uid="{8F8793D2-4111-9D4A-8A38-8D2824574D36}"/>
     <hyperlink ref="E91" r:id="rId48" xr:uid="{BE7994B6-39AC-456E-B133-6B1058FF6A77}"/>
     <hyperlink ref="E92" r:id="rId49" xr:uid="{243CF071-55CA-4C95-9A25-06902A0269E2}"/>
+    <hyperlink ref="E93:E94" r:id="rId50" display="https://climate.esa.int/projects/precursors-for-aerosols-and-ozone/" xr:uid="{6F364096-C606-4711-A00C-9A2D10C640B6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="1.143700787401575" bottom="1.143700787401575" header="0.75" footer="0.75"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>

--- a/data/cci/cci-datatype.xlsx
+++ b/data/cci/cci-datatype.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{01B1F068-9F27-4445-8169-AA66171EBCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D6034F1-9226-4925-9409-8AC7A38D31A9}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{01B1F068-9F27-4445-8169-AA66171EBCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{581814DD-8142-46FE-90D6-22C4F0E0164F}"/>
   <bookViews>
-    <workbookView xWindow="9660" yWindow="4650" windowWidth="28800" windowHeight="15345" xr2:uid="{43594B32-44C5-1E42-8A39-9DE60AB9706E}"/>
+    <workbookView xWindow="38280" yWindow="-60" windowWidth="38640" windowHeight="21120" xr2:uid="{43594B32-44C5-1E42-8A39-9DE60AB9706E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="322">
   <si>
     <t>URI</t>
   </si>
@@ -968,6 +968,24 @@
   </si>
   <si>
     <t>HCHO</t>
+  </si>
+  <si>
+    <t>dtype_issp</t>
+  </si>
+  <si>
+    <t>integrated sea state parameters</t>
+  </si>
+  <si>
+    <t>ISSP</t>
+  </si>
+  <si>
+    <t>dtype_so2</t>
+  </si>
+  <si>
+    <t>SO2</t>
+  </si>
+  <si>
+    <t>sulphur dioxide</t>
   </si>
 </sst>
 </file>
@@ -1677,7 +1695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7EC9CB0-CBFC-714F-A334-253ED842CDDE}">
-  <dimension ref="A1:BL94"/>
+  <dimension ref="A1:BL96"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" style="4" customWidth="1"/>
@@ -3362,6 +3380,40 @@
       </c>
       <c r="E94" s="15" t="s">
         <v>306</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E95" s="15" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E96" s="16" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -3416,6 +3468,7 @@
     <hyperlink ref="E91" r:id="rId48" xr:uid="{BE7994B6-39AC-456E-B133-6B1058FF6A77}"/>
     <hyperlink ref="E92" r:id="rId49" xr:uid="{243CF071-55CA-4C95-9A25-06902A0269E2}"/>
     <hyperlink ref="E93:E94" r:id="rId50" display="https://climate.esa.int/projects/precursors-for-aerosols-and-ozone/" xr:uid="{6F364096-C606-4711-A00C-9A2D10C640B6}"/>
+    <hyperlink ref="E95" r:id="rId51" xr:uid="{1567520A-62A2-4543-99A1-6607522C89C1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="1.143700787401575" bottom="1.143700787401575" header="0.75" footer="0.75"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
